--- a/data/manualdata/_manualdata_master_gaming.xlsx
+++ b/data/manualdata/_manualdata_master_gaming.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\manualdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD2B37B-A565-4C8A-96E8-F24B03FAE4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640CFF9B-B04C-4B63-914E-556B3A0FB240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="5" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -266,27 +266,15 @@
     <t>https://www.coupang.com/vp/products/8790276970?itemId=25584164030&amp;vendorItemId=92575058855</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8826133206?itemId=25719248433&amp;vendorItemId=92708022379</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, R9 375HX/5060</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8758944787?itemId=25467752802&amp;vendorItemId=92460264359</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, U9 275HX/5070</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8771136679?itemId=25513329531&amp;vendorItemId=92505305899</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, R7 350/5070 Ti</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8771223830?itemId=25513732236&amp;vendorItemId=92505701532</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, U9 275HX/5070 Ti</t>
   </si>
   <si>
@@ -317,9 +305,6 @@
     <t>ROG 스트릭스 G16, U9 275HX/5080</t>
   </si>
   <si>
-    <t>https://www.coupang.com/vp/products/8763580498?itemId=25484221675&amp;vendorItemId=92476480219</t>
-  </si>
-  <si>
     <t>오멘 맥스 16, R9 375HX/5080</t>
   </si>
   <si>
@@ -390,9 +375,6 @@
   </si>
   <si>
     <t>헬리오스 네오 18, U9 275HX/5070 Ti</t>
-  </si>
-  <si>
-    <t>스트릭스 G16, R9 9955HX3D/5070 Ti</t>
   </si>
   <si>
     <t>리전 프로 5 16IAX10, U9 275HX/5070 Ti</t>
@@ -459,6 +441,53 @@
   </si>
   <si>
     <t>리전 프로 5 16IAX10, U9 275HX/5070</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠팡</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>dual</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8771136679?itemId=25513329531&amp;vendorItemId=92505305899</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8826133206?itemId=25719248433&amp;vendorItemId=92708022379</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8763580498?itemId=25484221675&amp;vendorItemId=92476480219</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8758944787?itemId=25467752802&amp;vendorItemId=92460264359</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8771223830?itemId=25513732236&amp;vendorItemId=92505701532</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>portability</t>
+  </si>
+  <si>
+    <t>display</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cpu_style</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>single</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROG 스트릭스 G16, R9 9955HX3D/5070 Ti</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1453,13 +1482,16 @@
   <dimension ref="A1:Z79"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="94.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.640625" customWidth="1"/>
     <col min="4" max="4" width="40.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.0703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.0703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
+    <col min="17" max="18" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.55000000000000004">
@@ -1479,7 +1511,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -1516,6 +1548,15 @@
       </c>
       <c r="R1" t="s">
         <v>13</v>
+      </c>
+      <c r="S1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T1" t="s">
+        <v>130</v>
+      </c>
+      <c r="U1" t="s">
+        <v>131</v>
       </c>
       <c r="Y1" t="s">
         <v>14</v>
@@ -1529,10 +1570,10 @@
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1548,6 +1589,18 @@
 )</f>
         <v>5070</v>
       </c>
+      <c r="N2">
+        <v>32</v>
+      </c>
+      <c r="O2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P2">
+        <v>1024</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
       <c r="R2" t="str" cm="1">
         <f t="array" ref="R2">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D2), {"16","18","14"}),
@@ -1555,6 +1608,15 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2">
+        <v>7</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
       <c r="Y2" t="s">
         <v>20</v>
       </c>
@@ -1564,10 +1626,10 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1583,6 +1645,18 @@
 )</f>
         <v>5060</v>
       </c>
+      <c r="N3">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3">
+        <v>1024</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
       <c r="R3" t="str" cm="1">
         <f t="array" ref="R3">IFERROR(
     LOOKUP(2^15, SEARCH({"16","18","14"}, D3), {"16","18","14"}),
@@ -1590,6 +1664,12 @@
 )</f>
         <v>18</v>
       </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>7</v>
+      </c>
       <c r="Y3" t="s">
         <v>20</v>
       </c>
@@ -1599,10 +1679,10 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1614,6 +1694,18 @@
       <c r="M4" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="N4">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4">
+        <v>1024</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
       </c>
       <c r="R4" t="str" cm="1">
         <f t="array" ref="R4">IFERROR(
@@ -1622,6 +1714,12 @@
 )</f>
         <v>18</v>
       </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>7</v>
+      </c>
       <c r="Y4" t="s">
         <v>20</v>
       </c>
@@ -1631,7 +1729,7 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
         <v>53</v>
@@ -1646,6 +1744,18 @@
       <c r="M5" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="N5">
+        <v>16</v>
+      </c>
+      <c r="O5" t="s">
+        <v>132</v>
+      </c>
+      <c r="P5">
+        <v>512</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
       </c>
       <c r="R5" t="str" cm="1">
         <f t="array" ref="R5">IFERROR(
@@ -1654,6 +1764,12 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
+      <c r="T5">
+        <v>7</v>
+      </c>
       <c r="Y5" t="s">
         <v>20</v>
       </c>
@@ -1663,10 +1779,10 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1678,6 +1794,18 @@
       <c r="M6" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="N6">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>123</v>
+      </c>
+      <c r="P6">
+        <v>1024</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
       </c>
       <c r="R6" t="str" cm="1">
         <f t="array" ref="R6">IFERROR(
@@ -1686,6 +1814,12 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="S6">
+        <v>6</v>
+      </c>
+      <c r="T6">
+        <v>9</v>
+      </c>
       <c r="Y6" t="s">
         <v>20</v>
       </c>
@@ -1695,10 +1829,10 @@
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1710,6 +1844,18 @@
       <c r="M7" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="N7">
+        <v>32</v>
+      </c>
+      <c r="O7" t="s">
+        <v>123</v>
+      </c>
+      <c r="P7">
+        <v>1024</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
       </c>
       <c r="R7" t="str" cm="1">
         <f t="array" ref="R7">IFERROR(
@@ -1718,16 +1864,22 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>8</v>
+      </c>
       <c r="Y7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="0"/>
@@ -1736,6 +1888,18 @@
       <c r="M8" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="N8">
+        <v>32</v>
+      </c>
+      <c r="O8" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8">
+        <v>1024</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
       </c>
       <c r="R8" t="str" cm="1">
         <f t="array" ref="R8">IFERROR(
@@ -1744,6 +1908,12 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <v>8</v>
+      </c>
       <c r="Y8" t="s">
         <v>20</v>
       </c>
@@ -1753,10 +1923,10 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1768,6 +1938,18 @@
       <c r="M9" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="N9">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>123</v>
+      </c>
+      <c r="P9">
+        <v>1024</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
       </c>
       <c r="R9" t="str" cm="1">
         <f t="array" ref="R9">IFERROR(
@@ -1776,19 +1958,25 @@
 )</f>
         <v>18</v>
       </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>8</v>
+      </c>
       <c r="Y9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1800,6 +1988,9 @@
       <c r="M10" t="str">
         <f t="shared" si="1"/>
         <v>5080</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
       </c>
       <c r="R10" t="str" cm="1">
         <f t="array" ref="R10">IFERROR(
@@ -1817,10 +2008,10 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1832,6 +2023,9 @@
       <c r="M11" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
       </c>
       <c r="R11" t="str" cm="1">
         <f t="array" ref="R11">IFERROR(
@@ -1849,10 +2043,10 @@
         <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1864,6 +2058,9 @@
       <c r="M12" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
       </c>
       <c r="R12" t="str" cm="1">
         <f t="array" ref="R12">IFERROR(
@@ -1881,7 +2078,7 @@
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
         <v>31</v>
@@ -1902,6 +2099,9 @@
       <c r="M13" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
       </c>
       <c r="R13" t="str" cm="1">
         <f t="array" ref="R13">IFERROR(
@@ -1919,7 +2119,7 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
         <v>31</v>
@@ -1940,6 +2140,9 @@
       <c r="M14" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
       </c>
       <c r="R14" t="str" cm="1">
         <f t="array" ref="R14">IFERROR(
@@ -1957,7 +2160,7 @@
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
         <v>33</v>
@@ -1972,6 +2175,9 @@
       <c r="M15" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
       </c>
       <c r="R15" t="str" cm="1">
         <f t="array" ref="R15">IFERROR(
@@ -1989,7 +2195,7 @@
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>42</v>
@@ -2004,6 +2210,9 @@
       <c r="M16" t="str">
         <f t="shared" si="1"/>
         <v>5050</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
       </c>
       <c r="R16" t="str" cm="1">
         <f t="array" ref="R16">IFERROR(
@@ -2021,7 +2230,7 @@
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
@@ -2036,6 +2245,9 @@
       <c r="M17" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
       </c>
       <c r="R17" t="str" cm="1">
         <f t="array" ref="R17">IFERROR(
@@ -2053,10 +2265,10 @@
         <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2068,6 +2280,9 @@
       <c r="M18" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
       </c>
       <c r="R18" t="str" cm="1">
         <f t="array" ref="R18">IFERROR(
@@ -2085,7 +2300,7 @@
         <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -2100,6 +2315,9 @@
       <c r="M19" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
       </c>
       <c r="R19" t="str" cm="1">
         <f t="array" ref="R19">IFERROR(
@@ -2117,10 +2335,10 @@
         <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2132,6 +2350,9 @@
       <c r="M20" t="str">
         <f t="shared" si="1"/>
         <v>5050</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
       </c>
       <c r="R20" t="str" cm="1">
         <f t="array" ref="R20">IFERROR(
@@ -2149,10 +2370,10 @@
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2164,6 +2385,9 @@
       <c r="M21" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
       </c>
       <c r="R21" t="str" cm="1">
         <f t="array" ref="R21">IFERROR(
@@ -2178,13 +2402,13 @@
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2196,6 +2420,9 @@
       <c r="M22" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
       </c>
       <c r="R22" t="str" cm="1">
         <f t="array" ref="R22">IFERROR(
@@ -2213,10 +2440,10 @@
         <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2228,6 +2455,9 @@
       <c r="M23" t="str">
         <f t="shared" si="1"/>
         <v>5050</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
       </c>
       <c r="R23" t="str" cm="1">
         <f t="array" ref="R23">IFERROR(
@@ -2245,10 +2475,10 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2260,6 +2490,9 @@
       <c r="M24" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
       </c>
       <c r="R24" t="str" cm="1">
         <f t="array" ref="R24">IFERROR(
@@ -2277,10 +2510,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2292,6 +2525,9 @@
       <c r="M25" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
       </c>
       <c r="R25" t="str" cm="1">
         <f t="array" ref="R25">IFERROR(
@@ -2309,10 +2545,10 @@
         <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -2327,6 +2563,9 @@
       <c r="M26" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
       </c>
       <c r="R26" t="str" cm="1">
         <f t="array" ref="R26">IFERROR(
@@ -2335,16 +2574,19 @@
 )</f>
         <v>16</v>
       </c>
+      <c r="Y26" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>60</v>
@@ -2362,6 +2604,9 @@
       <c r="M27" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
       </c>
       <c r="R27" t="str" cm="1">
         <f t="array" ref="R27">IFERROR(
@@ -2376,13 +2621,13 @@
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2394,6 +2639,9 @@
       <c r="M28" t="str">
         <f t="shared" si="1"/>
         <v>4060</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
       </c>
       <c r="R28" t="str" cm="1">
         <f t="array" ref="R28">IFERROR(
@@ -2408,13 +2656,13 @@
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2426,6 +2674,9 @@
       <c r="M29" t="str">
         <f t="shared" si="1"/>
         <v>4060</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
       </c>
       <c r="R29" t="str" cm="1">
         <f t="array" ref="R29">IFERROR(
@@ -2440,13 +2691,13 @@
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2458,6 +2709,9 @@
       <c r="M30" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
       </c>
       <c r="R30" t="str" cm="1">
         <f t="array" ref="R30">IFERROR(
@@ -2472,10 +2726,10 @@
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
@@ -2490,6 +2744,9 @@
       <c r="M31" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
       </c>
       <c r="R31" t="str" cm="1">
         <f t="array" ref="R31">IFERROR(
@@ -2507,7 +2764,7 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -2522,6 +2779,9 @@
       <c r="M32" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
       </c>
       <c r="R32" t="str" cm="1">
         <f t="array" ref="R32">IFERROR(
@@ -2539,7 +2799,7 @@
         <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
@@ -2554,6 +2814,9 @@
       <c r="M33" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
       </c>
       <c r="R33" t="str" cm="1">
         <f t="array" ref="R33">IFERROR(
@@ -2568,13 +2831,13 @@
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2586,6 +2849,9 @@
       <c r="M34" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
       </c>
       <c r="R34" t="str" cm="1">
         <f t="array" ref="R34">IFERROR(
@@ -2600,13 +2866,13 @@
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -2618,6 +2884,9 @@
       <c r="M35" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
       </c>
       <c r="R35" t="str" cm="1">
         <f t="array" ref="R35">IFERROR(
@@ -2632,13 +2901,13 @@
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -2650,6 +2919,9 @@
       <c r="M36" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
       </c>
       <c r="R36" t="str" cm="1">
         <f t="array" ref="R36">IFERROR(
@@ -2663,14 +2935,14 @@
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" t="s">
-        <v>71</v>
+      <c r="B37" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2682,6 +2954,9 @@
       <c r="M37" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
       </c>
       <c r="R37" t="str" cm="1">
         <f t="array" ref="R37">IFERROR(
@@ -2695,15 +2970,15 @@
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" t="s">
         <v>67</v>
       </c>
-      <c r="C38" t="s">
-        <v>125</v>
-      </c>
-      <c r="D38" t="s">
-        <v>68</v>
-      </c>
       <c r="H38">
         <v>0</v>
       </c>
@@ -2714,6 +2989,9 @@
       <c r="M38" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
       </c>
       <c r="R38" t="str" cm="1">
         <f t="array" ref="R38">IFERROR(
@@ -2727,14 +3005,14 @@
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" t="s">
-        <v>84</v>
+      <c r="B39" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2746,6 +3024,9 @@
       <c r="M39" t="str">
         <f t="shared" si="1"/>
         <v>5080</v>
+      </c>
+      <c r="Q39">
+        <v>1</v>
       </c>
       <c r="R39" t="str" cm="1">
         <f t="array" ref="R39">IFERROR(
@@ -2759,14 +3040,14 @@
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" t="s">
-        <v>69</v>
+      <c r="B40" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2778,6 +3059,9 @@
       <c r="M40" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
       </c>
       <c r="R40" t="str" cm="1">
         <f t="array" ref="R40">IFERROR(
@@ -2791,14 +3075,14 @@
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" t="s">
-        <v>73</v>
+      <c r="B41" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2810,6 +3094,9 @@
       <c r="M41" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q41">
+        <v>1</v>
       </c>
       <c r="R41" t="str" cm="1">
         <f t="array" ref="R41">IFERROR(
@@ -2827,7 +3114,7 @@
         <v>19</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
@@ -2869,7 +3156,7 @@
     <row r="43" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="2"/>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
         <v>23</v>
@@ -2884,6 +3171,9 @@
       <c r="M43" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
       </c>
       <c r="R43" t="str" cm="1">
         <f t="array" ref="R43">IFERROR(
@@ -2899,7 +3189,7 @@
     <row r="44" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="1"/>
       <c r="C44" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
         <v>24</v>
@@ -2914,6 +3204,9 @@
       <c r="M44" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
       </c>
       <c r="R44" t="str" cm="1">
         <f t="array" ref="R44">IFERROR(
@@ -2931,10 +3224,10 @@
         <v>63</v>
       </c>
       <c r="C45" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -2946,6 +3239,9 @@
       <c r="M45" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
       </c>
       <c r="R45" t="str" cm="1">
         <f t="array" ref="R45">IFERROR(
@@ -2963,10 +3259,10 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2978,6 +3274,9 @@
       <c r="M46" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
       </c>
       <c r="R46" t="str" cm="1">
         <f t="array" ref="R46">IFERROR(
@@ -2995,10 +3294,10 @@
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -3010,6 +3309,9 @@
       <c r="M47" t="str">
         <f t="shared" si="1"/>
         <v>5070</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
       </c>
       <c r="R47" t="str" cm="1">
         <f t="array" ref="R47">IFERROR(
@@ -3024,13 +3326,13 @@
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -3042,6 +3344,9 @@
       <c r="M48" t="str">
         <f t="shared" si="1"/>
         <v>5080</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
       </c>
       <c r="R48" t="str" cm="1">
         <f t="array" ref="R48">IFERROR(
@@ -3059,10 +3364,10 @@
         <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -3074,6 +3379,9 @@
       <c r="M49" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
       </c>
       <c r="R49" t="str" cm="1">
         <f t="array" ref="R49">IFERROR(
@@ -3088,13 +3396,13 @@
     </row>
     <row r="50" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -3106,6 +3414,9 @@
       <c r="M50" t="str">
         <f t="shared" si="1"/>
         <v>5080</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
       </c>
       <c r="R50" t="str" cm="1">
         <f t="array" ref="R50">IFERROR(
@@ -3120,13 +3431,13 @@
     </row>
     <row r="51" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -3138,6 +3449,9 @@
       <c r="M51" t="str">
         <f t="shared" si="1"/>
         <v>5070 Ti</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
       </c>
       <c r="R51" t="str" cm="1">
         <f t="array" ref="R51">IFERROR(
@@ -3152,13 +3466,13 @@
     </row>
     <row r="52" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -3170,6 +3484,9 @@
       <c r="M52" t="str">
         <f t="shared" si="1"/>
         <v>5080</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
       </c>
       <c r="R52" t="str" cm="1">
         <f t="array" ref="R52">IFERROR(
@@ -3184,13 +3501,13 @@
     </row>
     <row r="53" spans="2:25" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -3202,6 +3519,9 @@
       <c r="M53" t="str">
         <f t="shared" si="1"/>
         <v>5060</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
       </c>
       <c r="R53" t="str" cm="1">
         <f t="array" ref="R53">IFERROR(
@@ -3433,8 +3753,13 @@
     <hyperlink ref="B29" r:id="rId3" xr:uid="{E0EA8A93-D050-4C50-ACA6-441A807B8EC8}"/>
     <hyperlink ref="B53" r:id="rId4" xr:uid="{177F6F5F-0535-4E51-AF80-40FAD6692204}"/>
     <hyperlink ref="B22" r:id="rId5" xr:uid="{AC6BDA1E-5D0A-4E27-9C9F-67AA96241FBD}"/>
+    <hyperlink ref="B37" r:id="rId6" xr:uid="{8F789FFB-30E1-4A9C-8DB1-A0A586952DC1}"/>
+    <hyperlink ref="B38" r:id="rId7" xr:uid="{8F2B78F5-0B48-4CE2-B9C9-3A2E4F5A4CDC}"/>
+    <hyperlink ref="B39" r:id="rId8" xr:uid="{A692DDC2-E1C6-4656-A2ED-5353E8769756}"/>
+    <hyperlink ref="B40" r:id="rId9" xr:uid="{89C32D61-1759-4DC4-9BB7-7043F4AB8240}"/>
+    <hyperlink ref="B41" r:id="rId10" xr:uid="{973916E0-65EB-425C-8E76-C83165B3C79C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>